--- a/HolidayCalendarService/Template/Power Platform und Teams English.xlsx
+++ b/HolidayCalendarService/Template/Power Platform und Teams English.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicoschreder\Development\adventcalendarapp\HolidayCalendarService\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E310DE3C-2C29-4B37-A2C9-5F9988F91FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AB0128-53EC-4B89-A76B-06FFCF55F3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{DA429942-75DC-4399-AA24-F29984099B9A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="55">
   <si>
     <t>publishDate</t>
   </si>
@@ -163,13 +163,52 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=2dscy89ks9I</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Power%20Platform%20%2B%20Teams%20English/1.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Power%20Platform%20%2B%20Teams%20English/3.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Power%20Platform%20%2B%20Teams%20English/5.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Power%20Platform%20%2B%20Teams%20English/7.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Power%20Platform%20%2B%20Teams%20English/9.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Power%20Platform%20%2B%20Teams%20English/11.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Power%20Platform%20%2B%20Teams%20English/13.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Power%20Platform%20%2B%20Teams%20English/15.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Power%20Platform%20%2B%20Teams%20English/17.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Power%20Platform%20%2B%20Teams%20English/19.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Power%20Platform%20%2B%20Teams%20English/21.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Power%20Platform%20%2B%20Teams%20English/23.jpg</t>
+  </si>
+  <si>
+    <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Power%20Platform%20%2B%20Teams%20English/24.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -179,14 +218,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -209,17 +240,14 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -560,7 +588,7 @@
   <cols>
     <col min="1" max="1" width="58.90625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="84.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="132.6328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -585,7 +613,9 @@
       <c r="B2" s="1">
         <v>44896</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" t="s">
+        <v>42</v>
+      </c>
       <c r="D2" t="s">
         <v>4</v>
       </c>
@@ -597,7 +627,7 @@
       <c r="B3" s="1">
         <v>44897</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
       <c r="D3" t="s">
@@ -611,7 +641,9 @@
       <c r="B4" s="1">
         <v>44898</v>
       </c>
-      <c r="C4" s="2"/>
+      <c r="C4" t="s">
+        <v>43</v>
+      </c>
       <c r="D4" t="s">
         <v>4</v>
       </c>
@@ -623,7 +655,7 @@
       <c r="B5" s="1">
         <v>44899</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>32</v>
       </c>
       <c r="D5" t="s">
@@ -637,7 +669,9 @@
       <c r="B6" s="1">
         <v>44900</v>
       </c>
-      <c r="C6" s="2"/>
+      <c r="C6" t="s">
+        <v>44</v>
+      </c>
       <c r="D6" t="s">
         <v>4</v>
       </c>
@@ -649,7 +683,7 @@
       <c r="B7" s="1">
         <v>44901</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>33</v>
       </c>
       <c r="D7" t="s">
@@ -663,7 +697,9 @@
       <c r="B8" s="1">
         <v>44902</v>
       </c>
-      <c r="C8" s="2"/>
+      <c r="C8" t="s">
+        <v>45</v>
+      </c>
       <c r="D8" t="s">
         <v>4</v>
       </c>
@@ -675,7 +711,7 @@
       <c r="B9" s="1">
         <v>44903</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>34</v>
       </c>
       <c r="D9" t="s">
@@ -689,7 +725,9 @@
       <c r="B10" s="1">
         <v>44904</v>
       </c>
-      <c r="C10" s="2"/>
+      <c r="C10" t="s">
+        <v>46</v>
+      </c>
       <c r="D10" t="s">
         <v>4</v>
       </c>
@@ -701,7 +739,7 @@
       <c r="B11" s="1">
         <v>44905</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" t="s">
         <v>35</v>
       </c>
       <c r="D11" t="s">
@@ -715,7 +753,9 @@
       <c r="B12" s="1">
         <v>44906</v>
       </c>
-      <c r="C12" s="2"/>
+      <c r="C12" t="s">
+        <v>47</v>
+      </c>
       <c r="D12" t="s">
         <v>4</v>
       </c>
@@ -727,7 +767,7 @@
       <c r="B13" s="1">
         <v>44907</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" t="s">
         <v>36</v>
       </c>
       <c r="D13" t="s">
@@ -741,7 +781,9 @@
       <c r="B14" s="1">
         <v>44908</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
       <c r="D14" t="s">
         <v>4</v>
       </c>
@@ -753,7 +795,7 @@
       <c r="B15" s="1">
         <v>44909</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" t="s">
         <v>37</v>
       </c>
       <c r="D15" t="s">
@@ -767,6 +809,9 @@
       <c r="B16" s="1">
         <v>44910</v>
       </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
       <c r="D16" t="s">
         <v>4</v>
       </c>
@@ -778,7 +823,7 @@
       <c r="B17" s="1">
         <v>44911</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" t="s">
         <v>38</v>
       </c>
       <c r="D17" t="s">
@@ -792,7 +837,9 @@
       <c r="B18" s="1">
         <v>44912</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
       <c r="D18" t="s">
         <v>4</v>
       </c>
@@ -804,7 +851,7 @@
       <c r="B19" s="1">
         <v>44913</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" t="s">
         <v>39</v>
       </c>
       <c r="D19" t="s">
@@ -818,7 +865,9 @@
       <c r="B20" s="1">
         <v>44914</v>
       </c>
-      <c r="C20" s="2"/>
+      <c r="C20" t="s">
+        <v>51</v>
+      </c>
       <c r="D20" t="s">
         <v>4</v>
       </c>
@@ -830,7 +879,7 @@
       <c r="B21" s="1">
         <v>44915</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" t="s">
         <v>40</v>
       </c>
       <c r="D21" t="s">
@@ -844,7 +893,9 @@
       <c r="B22" s="1">
         <v>44916</v>
       </c>
-      <c r="C22" s="2"/>
+      <c r="C22" t="s">
+        <v>52</v>
+      </c>
       <c r="D22" t="s">
         <v>4</v>
       </c>
@@ -856,7 +907,7 @@
       <c r="B23" s="1">
         <v>44917</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" t="s">
         <v>41</v>
       </c>
       <c r="D23" t="s">
@@ -870,7 +921,9 @@
       <c r="B24" s="1">
         <v>44918</v>
       </c>
-      <c r="C24" s="2"/>
+      <c r="C24" t="s">
+        <v>53</v>
+      </c>
       <c r="D24" t="s">
         <v>4</v>
       </c>
@@ -882,30 +935,19 @@
       <c r="B25" s="1">
         <v>44919</v>
       </c>
-      <c r="C25" s="2"/>
+      <c r="C25" t="s">
+        <v>54</v>
+      </c>
       <c r="D25" t="s">
         <v>4</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <hyperlinks>
-    <hyperlink ref="C7" r:id="rId1" xr:uid="{9D70A3C8-8198-4E02-9DAC-ECA0CA3B941C}"/>
-    <hyperlink ref="C17" r:id="rId2" xr:uid="{0EFE390A-E071-43D4-97A2-C6ACA3BB4D7A}"/>
-    <hyperlink ref="C3" r:id="rId3" xr:uid="{63A27322-FD80-4EF8-A5F5-D0B19657FFFA}"/>
-    <hyperlink ref="C5" r:id="rId4" xr:uid="{3DA3BF52-D7EF-4ACC-B94B-B5905485DFD0}"/>
-    <hyperlink ref="C9" r:id="rId5" xr:uid="{C1D8D7DB-CBA5-4587-8F63-6A1A32E966C7}"/>
-    <hyperlink ref="C11" r:id="rId6" xr:uid="{629561AA-C605-44D0-92DC-906BD99B4C02}"/>
-    <hyperlink ref="C13" r:id="rId7" xr:uid="{CEC8D436-4BE0-43CD-821A-6B998EFA735A}"/>
-    <hyperlink ref="C15" r:id="rId8" location="design-your-app-in-figma" xr:uid="{68AE2349-4430-4DB7-A863-99805DE47577}"/>
-    <hyperlink ref="C19" r:id="rId9" xr:uid="{A3901757-4C11-46EA-B756-E68797DDA3D1}"/>
-    <hyperlink ref="C21" r:id="rId10" xr:uid="{A6D86229-6F05-4F52-ACB6-DC873679AE20}"/>
-    <hyperlink ref="C23" r:id="rId11" xr:uid="{EBA7CB4A-078C-46F2-A498-2BE3AE8CFCF9}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId12"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart r:id="rId13"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">

--- a/HolidayCalendarService/Template/Power Platform und Teams English.xlsx
+++ b/HolidayCalendarService/Template/Power Platform und Teams English.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicoschreder\Development\adventcalendarapp\HolidayCalendarService\Template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AB0128-53EC-4B89-A76B-06FFCF55F3DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5053C2-9251-410F-8D3C-EA3E08FF1EBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{DA429942-75DC-4399-AA24-F29984099B9A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="56">
   <si>
     <t>publishDate</t>
   </si>
@@ -202,6 +202,9 @@
   </si>
   <si>
     <t>https://raw.githubusercontent.com/nschreder/holidaycalendarapp/main/HolidayCalendarService/Power%20Platform%20%2B%20Teams%20English/24.jpg</t>
+  </si>
+  <si>
+    <t>Managing your notifications with quite hours</t>
   </si>
 </sst>
 </file>
@@ -720,7 +723,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="B10" s="1">
         <v>44904</v>
@@ -951,7 +954,7 @@
   </tableParts>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E0A89A54-F0B3-4D21-8D2D-CA14DB1D7630}">
           <x14:formula1>
             <xm:f>Values!$A$2:$A$4</xm:f>
